--- a/docs/collections/ichiko/metadata/data.xlsx
+++ b/docs/collections/ichiko/metadata/data.xlsx
@@ -2072,7 +2072,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ichiko/document/2f2164d1-0f3c-01c8-42b5-33df058328a2</t>
   </si>
   <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5877e3e82ce6bf75573056d27593b14fc8432c2b.jpg</t>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5953ac09f57859bc5f81dfbc3b991c2ab247197e.jpg</t>
   </si>
   <si>
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1038820</t>
@@ -2153,7 +2153,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ichiko/document/4120a330-2f1c-4e2c-5d48-21aed4d42704</t>
   </si>
   <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/36e6583cc4fe7dca8d9f27de049ea9331aa58629.jpg</t>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c884706cd13b309079c21d0f01b61ed11a2dd908.jpg</t>
   </si>
   <si>
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1038824</t>

--- a/docs/collections/ichiko/metadata/data.xlsx
+++ b/docs/collections/ichiko/metadata/data.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>所蔵図書館室 / Holding Library</t>
+          <t>所蔵図書館室/Holding Library</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
